--- a/exports/IREDA_full_report.xlsx
+++ b/exports/IREDA_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>18.66</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45286.55208333334</v>
+        <v>45287.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>102.2</v>
+        <v>98.95</v>
       </c>
       <c r="I2" t="n">
         <v>101.4269669557492</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K2" t="n">
-        <v>63.39</v>
+        <v>58.19</v>
       </c>
       <c r="L2" t="n">
         <v>1.68</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>18.86</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45303.55208333334</v>
+        <v>45306.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>110</v>
+        <v>121.8</v>
       </c>
       <c r="I3" t="n">
         <v>110.2846911345012</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.17</v>
+        <v>-23.09</v>
       </c>
       <c r="L3" t="n">
-        <v>13.69</v>
+        <v>23.09</v>
       </c>
       <c r="M3" t="n">
         <v>1.76</v>
       </c>
       <c r="N3" t="n">
-        <v>6.23</v>
+        <v>10.73</v>
       </c>
       <c r="O3" t="n">
         <v>-2.3</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>13.95</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45330.55208333334</v>
+        <v>45331.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>189.05</v>
+        <v>179.6</v>
       </c>
       <c r="I4" t="n">
         <v>184.5757806910413</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K4" t="n">
-        <v>55.21</v>
+        <v>47.45</v>
       </c>
       <c r="L4" t="n">
         <v>8.369999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>4.52</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
         <v>5</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>12.41</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45336.55208333334</v>
+        <v>45337.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>170.25</v>
+        <v>177.05</v>
       </c>
       <c r="I5" t="n">
         <v>172.1492839766247</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>5.21</v>
+        <v>1.42</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="N5" t="n">
         <v>5</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>11.9</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45345.55208333334</v>
+        <v>45348.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>159.45</v>
+        <v>151.5</v>
       </c>
       <c r="I6" t="n">
         <v>158.5237707217607</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>-9.94</v>
+        <v>-14.43</v>
       </c>
       <c r="L6" t="n">
-        <v>9.94</v>
+        <v>14.43</v>
       </c>
       <c r="M6" t="n">
-        <v>4.15</v>
+        <v>4.99</v>
       </c>
       <c r="N6" t="n">
         <v>5.03</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.72</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45373.55208333334</v>
+        <v>45377.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>138.65</v>
+        <v>142.35</v>
       </c>
       <c r="I7" t="n">
         <v>140.836746734034</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K7" t="n">
-        <v>8.48</v>
+        <v>6.04</v>
       </c>
       <c r="L7" t="n">
         <v>6.14</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>172.45</v>
+        <v>167</v>
       </c>
       <c r="I8" t="n">
         <v>167.0553368667751</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K8" t="n">
-        <v>21.15</v>
+        <v>17.32</v>
       </c>
       <c r="L8" t="n">
         <v>5.16</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>12.55</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45430.38541666666</v>
+        <v>45433.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>176</v>
+        <v>182.9</v>
       </c>
       <c r="I9" t="n">
         <v>178.3311688413538</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.39</v>
+        <v>-9.52</v>
       </c>
       <c r="L9" t="n">
-        <v>6.89</v>
+        <v>10.66</v>
       </c>
       <c r="M9" t="n">
         <v>1.19</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>192.5</v>
+        <v>170.65</v>
       </c>
       <c r="I10" t="n">
         <v>176.563681235974</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>5.25</v>
+        <v>-6.7</v>
       </c>
       <c r="L10" t="n">
-        <v>4.54</v>
+        <v>15.8</v>
       </c>
       <c r="M10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="N10" t="n">
-        <v>4.51</v>
+        <v>12.57</v>
       </c>
       <c r="O10" t="n">
         <v>4.52</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>16.95</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45464.38541666666</v>
+        <v>45464.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>183.5</v>
+        <v>190.1</v>
       </c>
       <c r="I11" t="n">
         <v>188.6765095627389</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-7.53</v>
+        <v>-11.4</v>
       </c>
       <c r="L11" t="n">
-        <v>11.34</v>
+        <v>11.92</v>
       </c>
       <c r="M11" t="n">
         <v>2.02</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>254.8</v>
+        <v>239</v>
       </c>
       <c r="I12" t="n">
         <v>253.1549616279733</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>42</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K12" t="n">
-        <v>34.03</v>
+        <v>25.72</v>
       </c>
       <c r="L12" t="n">
         <v>3.98</v>
       </c>
       <c r="M12" t="n">
-        <v>2.01</v>
+        <v>5.04</v>
       </c>
       <c r="N12" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="O12" t="n">
         <v>7.1</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>11.89</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45525.55208333334</v>
+        <v>45526.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>239.1</v>
+        <v>261.95</v>
       </c>
       <c r="I13" t="n">
         <v>254.8497089786095</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.04</v>
+        <v>-9.6</v>
       </c>
       <c r="L13" t="n">
-        <v>5.86</v>
+        <v>11.17</v>
       </c>
       <c r="M13" t="n">
         <v>3.8</v>
       </c>
       <c r="N13" t="n">
-        <v>5.08</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-6.53</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>10.75</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45534.55208333334</v>
+        <v>45537.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>240</v>
+        <v>235.73</v>
       </c>
       <c r="I14" t="n">
         <v>239.4229329434846</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.380000000000001</v>
+        <v>-10.01</v>
       </c>
       <c r="L14" t="n">
-        <v>9.119999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="M14" t="n">
         <v>0.02</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.09</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45574.38541666666</v>
+        <v>45574.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>227.95</v>
+        <v>232.5</v>
       </c>
       <c r="I15" t="n">
         <v>229.855786116088</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>37</v>
+        <v>37.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3</v>
+        <v>1.37</v>
       </c>
       <c r="L15" t="n">
         <v>2.38</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.9</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45583.38541666666</v>
+        <v>45583.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>218.05</v>
+        <v>215.99</v>
       </c>
       <c r="I16" t="n">
         <v>216.2049996036121</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.22</v>
+        <v>-7.1</v>
       </c>
       <c r="L16" t="n">
         <v>9.09</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.9</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45594.55208333334</v>
+        <v>45595.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>205.5</v>
+        <v>210.17</v>
       </c>
       <c r="I17" t="n">
         <v>210.023221002983</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>4.86</v>
+        <v>2.69</v>
       </c>
       <c r="L17" t="n">
         <v>1.18</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>11.28</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45608.38541666666</v>
+        <v>45608.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>196.2</v>
+        <v>194.15</v>
       </c>
       <c r="I18" t="n">
         <v>194.4732344769493</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.65</v>
+        <v>-7.62</v>
       </c>
       <c r="L18" t="n">
-        <v>6.74</v>
+        <v>8.07</v>
       </c>
       <c r="M18" t="n">
         <v>0.54</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>7.6</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45623.38541666666</v>
+        <v>45623.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>193.7</v>
+        <v>198.4</v>
       </c>
       <c r="I19" t="n">
         <v>197.5942452380969</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>0.23</v>
+        <v>-2.19</v>
       </c>
       <c r="L19" t="n">
-        <v>1.26</v>
+        <v>2.19</v>
       </c>
       <c r="M19" t="n">
         <v>3.5</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>212.29</v>
+        <v>208.1</v>
       </c>
       <c r="I20" t="n">
         <v>209.1704677506687</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>4.89</v>
       </c>
       <c r="L20" t="n">
         <v>2.57</v>
@@ -1581,7 +1820,7 @@
         <v>0.88</v>
       </c>
       <c r="N20" t="n">
-        <v>2.05</v>
+        <v>2.54</v>
       </c>
       <c r="O20" t="n">
         <v>3.98</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>7.62</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45656.38541666666</v>
+        <v>45656.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>203.05</v>
+        <v>217.24</v>
       </c>
       <c r="I21" t="n">
         <v>209.5219426054317</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>2.43</v>
+        <v>-4.39</v>
       </c>
       <c r="L21" t="n">
-        <v>2.81</v>
+        <v>6.92</v>
       </c>
       <c r="M21" t="n">
         <v>0.79</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.78</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45666.55208333334</v>
+        <v>45667.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>215.1</v>
+        <v>206.2</v>
       </c>
       <c r="I22" t="n">
         <v>210.7385198204138</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.99</v>
+        <v>-5.08</v>
       </c>
       <c r="L22" t="n">
         <v>6.97</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>15.9</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45688.38541666666</v>
+        <v>45688.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>201.1</v>
+        <v>202.11</v>
       </c>
       <c r="I23" t="n">
         <v>201.6166537673608</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K23" t="n">
-        <v>2.47</v>
+        <v>1.98</v>
       </c>
       <c r="L23" t="n">
         <v>8.08</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45689.55208333334</v>
+        <v>45691.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>194.5</v>
+        <v>184.35</v>
       </c>
       <c r="I24" t="n">
         <v>185.342273560698</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.77</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>5.07</v>
+        <v>9.06</v>
       </c>
       <c r="M24" t="n">
-        <v>0.03</v>
+        <v>2.69</v>
       </c>
       <c r="N24" t="n">
-        <v>3.77</v>
+        <v>3.91</v>
       </c>
       <c r="O24" t="n">
         <v>2.96</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.7</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45708.55208333334</v>
+        <v>45709.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>173.1</v>
+        <v>180.83</v>
       </c>
       <c r="I25" t="n">
         <v>176.4356804639533</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K25" t="n">
-        <v>6.1</v>
+        <v>1.91</v>
       </c>
       <c r="L25" t="n">
         <v>6.54</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>10.97</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45715.55208333334</v>
+        <v>45716.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>165.62</v>
+        <v>153.09</v>
       </c>
       <c r="I26" t="n">
         <v>160.9969253928402</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>-8.41</v>
+        <v>-15.34</v>
       </c>
       <c r="L26" t="n">
-        <v>8.48</v>
+        <v>16.22</v>
       </c>
       <c r="M26" t="n">
-        <v>0.62</v>
+        <v>2.79</v>
       </c>
       <c r="N26" t="n">
-        <v>4.65</v>
+        <v>5.45</v>
       </c>
       <c r="O26" t="n">
         <v>1.68</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>14.54</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>147.2</v>
+        <v>152.16</v>
       </c>
       <c r="I27" t="n">
         <v>149.5101222636272</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>0.61</v>
       </c>
       <c r="L27" t="n">
         <v>6.04</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.710000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>162.07</v>
+        <v>156.31</v>
       </c>
       <c r="I28" t="n">
         <v>156.9581424267602</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K28" t="n">
-        <v>6.51</v>
+        <v>2.73</v>
       </c>
       <c r="L28" t="n">
         <v>3.36</v>
@@ -2037,7 +2372,7 @@
         <v>1.49</v>
       </c>
       <c r="N28" t="n">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="O28" t="n">
         <v>2.93</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>10.69</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>154.25</v>
+        <v>162.32</v>
       </c>
       <c r="I29" t="n">
         <v>161.4850424662812</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
-        <v>1.32</v>
+        <v>-3.84</v>
       </c>
       <c r="L29" t="n">
-        <v>4.02</v>
+        <v>4.38</v>
       </c>
       <c r="M29" t="n">
         <v>3.63</v>
       </c>
       <c r="N29" t="n">
-        <v>2.01</v>
+        <v>9.02</v>
       </c>
       <c r="O29" t="n">
         <v>-3.28</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>10.07</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>166.1</v>
+        <v>164.51</v>
       </c>
       <c r="I30" t="n">
         <v>165.7595689861262</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K30" t="n">
-        <v>2.33</v>
+        <v>1.35</v>
       </c>
       <c r="L30" t="n">
         <v>2.29</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.18</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45789.38541666666</v>
+        <v>45789.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>165.6</v>
+        <v>168.45</v>
       </c>
       <c r="I31" t="n">
         <v>166.7248576286908</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.66</v>
+        <v>-2.39</v>
       </c>
       <c r="L31" t="n">
         <v>3.09</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>175.23</v>
+        <v>168.69</v>
       </c>
       <c r="I32" t="n">
         <v>173.1125556745939</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>4.02</v>
+        <v>0.14</v>
       </c>
       <c r="L32" t="n">
-        <v>1.86</v>
+        <v>3.37</v>
       </c>
       <c r="M32" t="n">
-        <v>1.47</v>
+        <v>4.7</v>
       </c>
       <c r="N32" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="O32" t="n">
         <v>6.68</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.01</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45832.55208333334</v>
+        <v>45833.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>166.06</v>
+        <v>170.94</v>
       </c>
       <c r="I33" t="n">
         <v>170.6768615684929</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K33" t="n">
-        <v>1.56</v>
+        <v>-1.33</v>
       </c>
       <c r="L33" t="n">
-        <v>0.86</v>
+        <v>1.55</v>
       </c>
       <c r="M33" t="n">
         <v>2.72</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>7.67</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>169.9</v>
+        <v>161.2</v>
       </c>
       <c r="I34" t="n">
         <v>162.6277163218083</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.61</v>
+        <v>-5.7</v>
       </c>
       <c r="L34" t="n">
-        <v>3.99</v>
+        <v>6.52</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2</v>
+        <v>5.24</v>
       </c>
       <c r="N34" t="n">
-        <v>1.38</v>
+        <v>5.83</v>
       </c>
       <c r="O34" t="n">
         <v>3.58</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.13</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45889.55208333334</v>
+        <v>45890.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>148.9</v>
+        <v>149.7</v>
       </c>
       <c r="I35" t="n">
         <v>149.3917874376955</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K35" t="n">
-        <v>7.63</v>
+        <v>7.13</v>
       </c>
       <c r="L35" t="n">
         <v>1.46</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>3.45</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45895.38541666666</v>
+        <v>45895.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>145.19</v>
+        <v>144.16</v>
       </c>
       <c r="I36" t="n">
         <v>144.5374366185913</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>-3.01</v>
+        <v>-3.7</v>
       </c>
       <c r="L36" t="n">
-        <v>3.41</v>
+        <v>3.94</v>
       </c>
       <c r="M36" t="n">
         <v>0.13</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>4.72</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>145.46</v>
+        <v>148.54</v>
       </c>
       <c r="I37" t="n">
         <v>146.9985058135844</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.9</v>
+        <v>-3.04</v>
       </c>
       <c r="L37" t="n">
-        <v>2.52</v>
+        <v>3.43</v>
       </c>
       <c r="M37" t="n">
         <v>1.2</v>
       </c>
       <c r="N37" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="O37" t="n">
         <v>-2.69</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>5.09</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45924.38541666666</v>
+        <v>45924.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>153.92</v>
+        <v>152.37</v>
       </c>
       <c r="I38" t="n">
         <v>153.1269699982883</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>3.62</v>
+        <v>2.58</v>
       </c>
       <c r="L38" t="n">
         <v>2.09</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.2</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45943.55208333334</v>
+        <v>45944.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>150.15</v>
+        <v>155.27</v>
       </c>
       <c r="I39" t="n">
         <v>155.2142378775448</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>1.46</v>
+        <v>-1.9</v>
       </c>
       <c r="L39" t="n">
         <v>2.64</v>
@@ -2664,7 +3131,7 @@
         <v>1.66</v>
       </c>
       <c r="N39" t="n">
-        <v>2.41</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
         <v>-2.01</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.72</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45979.38541666666</v>
+        <v>45979.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>148.84</v>
+        <v>148.14</v>
       </c>
       <c r="I40" t="n">
         <v>148.1454871201427</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.14</v>
+        <v>-4.59</v>
       </c>
       <c r="L40" t="n">
         <v>5.81</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>4.23</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46013.55208333334</v>
+        <v>46014.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>135.6</v>
+        <v>139.59</v>
       </c>
       <c r="I41" t="n">
         <v>136.9763222846119</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>8.460000000000001</v>
+        <v>5.77</v>
       </c>
       <c r="L41" t="n">
         <v>0.66</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.92</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46031.38541666666</v>
+        <v>46031.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>137.85</v>
+        <v>137.1</v>
       </c>
       <c r="I42" t="n">
         <v>137.7979777150529</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.25</v>
+        <v>-1.78</v>
       </c>
       <c r="L42" t="n">
         <v>3.02</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>6.77</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>114.6</v>
+        <v>120.02</v>
       </c>
       <c r="I43" t="n">
         <v>119.3519776965296</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>74</v>
+        <v>74.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>16.41</v>
+        <v>12.46</v>
       </c>
       <c r="L43" t="n">
         <v>4.3</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46111.38541666666</v>
+        <v>46111.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>112.56</v>
+        <v>109</v>
       </c>
       <c r="I44" t="n">
         <v>110.8904659333069</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.22</v>
+        <v>-9.18</v>
       </c>
       <c r="L44" t="n">
-        <v>6.97</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M44" t="n">
         <v>0.95</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>10.02</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>115.72</v>
+        <v>121.45</v>
       </c>
       <c r="I45" t="n">
         <v>119.9177463011573</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.17</v>
+        <v>-11.42</v>
       </c>
       <c r="L45" t="n">
-        <v>6.42</v>
+        <v>12.06</v>
       </c>
       <c r="M45" t="n">
         <v>4.56</v>
       </c>
       <c r="N45" t="n">
-        <v>4.66</v>
+        <v>6.21</v>
       </c>
       <c r="O45" t="n">
         <v>-4.51</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.74</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>130.92</v>
+        <v>126.11</v>
       </c>
       <c r="I46" t="n">
         <v>130.068829615127</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K46" t="n">
-        <v>7.8</v>
+        <v>3.84</v>
       </c>
       <c r="L46" t="n">
         <v>2.53</v>
@@ -3063,7 +3614,7 @@
         <v>3.03</v>
       </c>
       <c r="N46" t="n">
-        <v>2.73</v>
+        <v>4.41</v>
       </c>
       <c r="O46" t="n">
         <v>6.21</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>8.06</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46171.38541666666</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>130.36</v>
+        <v>135.39</v>
       </c>
       <c r="I47" t="n">
         <v>133.1761471769368</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.37</v>
+        <v>-7.36</v>
       </c>
       <c r="L47" t="n">
-        <v>5.11</v>
+        <v>7.45</v>
       </c>
       <c r="M47" t="n">
         <v>1.16</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>7.21</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46174.55208333334</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>126.13</v>
+        <v>123.92</v>
       </c>
       <c r="I48" t="n">
         <v>125.6341176134189</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.84</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>7.29</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M48" t="n">
         <v>2.08</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>7.07</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>122.2</v>
+        <v>125.52</v>
       </c>
       <c r="I49" t="n">
         <v>124.6065789553057</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K49" t="n">
-        <v>1.39</v>
+        <v>-1.29</v>
       </c>
       <c r="L49" t="n">
-        <v>1.41</v>
+        <v>1.89</v>
       </c>
       <c r="M49" t="n">
-        <v>1.38</v>
+        <v>2.29</v>
       </c>
       <c r="N49" t="n">
         <v>3.19</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.76</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46210.55208333334</v>
+        <v>46211.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>125.4</v>
+        <v>124.02</v>
       </c>
       <c r="I50" t="n">
         <v>124.5891034620024</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.1</v>
+        <v>-1.2</v>
       </c>
       <c r="L50" t="n">
-        <v>0.88</v>
+        <v>1.93</v>
       </c>
       <c r="M50" t="n">
-        <v>0.61</v>
+        <v>0.76</v>
       </c>
       <c r="N50" t="n">
-        <v>2.82</v>
+        <v>3.43</v>
       </c>
       <c r="O50" t="n">
         <v>2.32</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>3.79</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46259.38541666666</v>
+        <v>46259.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>116.59</v>
+        <v>120.78</v>
       </c>
       <c r="I51" t="n">
         <v>117.9127020919137</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K51" t="n">
-        <v>5.99</v>
+        <v>2.61</v>
       </c>
       <c r="L51" t="n">
         <v>2.19</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>6.16</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>114.19</v>
+        <v>112.64</v>
       </c>
       <c r="I52" t="n">
         <v>113.3340618154327</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.46</v>
+        <v>-6.74</v>
       </c>
       <c r="L52" t="n">
-        <v>5.49</v>
+        <v>7.1</v>
       </c>
       <c r="M52" t="n">
         <v>2.31</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.8</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46289.55208333334</v>
+        <v>46290.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>110.06</v>
+        <v>113.28</v>
       </c>
       <c r="I53" t="n">
         <v>112.7292883390331</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K53" t="n">
-        <v>2.29</v>
+        <v>-0.57</v>
       </c>
       <c r="L53" t="n">
         <v>1.87</v>
@@ -3462,7 +4097,7 @@
         <v>0.85</v>
       </c>
       <c r="N53" t="n">
-        <v>2.65</v>
+        <v>3.01</v>
       </c>
       <c r="O53" t="n">
         <v>-1.61</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.01</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46296.55208333334</v>
+        <v>46300.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>111</v>
+        <v>108.97</v>
       </c>
       <c r="I54" t="n">
         <v>109.2989803286836</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.01</v>
+        <v>-3.8</v>
       </c>
       <c r="L54" t="n">
         <v>4.19</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3579,6 +4238,12 @@
       <c r="Q55" t="n">
         <v>32</v>
       </c>
+      <c r="R55" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4933,7 +5598,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18.4</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="6">
@@ -4943,7 +5608,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -4953,7 +5618,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74</v>
+        <v>74.8</v>
       </c>
     </row>
     <row r="8">
@@ -4963,7 +5628,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -4973,7 +5638,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -4983,7 +5648,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="11">
@@ -5023,7 +5688,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.48</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="15">
@@ -5033,7 +5698,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.05</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="16">
@@ -5043,7 +5708,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.85</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="17">
@@ -5053,7 +5718,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>63.39</v>
+        <v>58.19</v>
       </c>
     </row>
     <row r="18">
@@ -5063,7 +5728,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.7</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="19">
@@ -5073,7 +5738,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.6</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="20">
@@ -5083,7 +5748,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.02</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="21">
@@ -5093,7 +5758,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.69</v>
+        <v>23.09</v>
       </c>
     </row>
     <row r="22">
@@ -5103,7 +5768,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -5113,7 +5778,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -5123,7 +5788,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="25">
@@ -5143,7 +5808,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -5153,7 +5818,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.39</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="28">
@@ -5163,7 +5828,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
